--- a/Cost model data structure.xlsx
+++ b/Cost model data structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samst\OneDrive\Documents\Work\Projects\PMH web tool\Thailand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B37D8D0-8633-4366-8B46-6845354987DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB785F5-A9DD-4298-A728-6B3853AA5593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
   </bookViews>
@@ -6761,7 +6761,7 @@
         <v>1009</v>
       </c>
       <c r="E89" s="20">
-        <v>4375</v>
+        <v>526</v>
       </c>
       <c r="F89" s="35" t="s">
         <v>10</v>
@@ -6799,7 +6799,7 @@
         <v>1010</v>
       </c>
       <c r="E90" s="20">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="F90" s="35" t="s">
         <v>10</v>
@@ -6943,7 +6943,7 @@
         <v>1014</v>
       </c>
       <c r="E94" s="20">
-        <v>0</v>
+        <v>1193</v>
       </c>
       <c r="F94" s="35" t="s">
         <v>10</v>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="D745" s="8">
         <f>D149*inputs!E89</f>
-        <v>135866707.15723985</v>
+        <v>16335060.106219009</v>
       </c>
       <c r="E745" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="D746" s="8">
         <f>D150*inputs!E90</f>
-        <v>0</v>
+        <v>9518884.3226606343</v>
       </c>
       <c r="E746" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -22579,7 +22579,7 @@
       </c>
       <c r="D750" s="8">
         <f>D155*inputs!E94</f>
-        <v>0</v>
+        <v>32626546.958244383</v>
       </c>
       <c r="E750" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="E41" s="11">
         <f>SUM(computations!D745:D751)</f>
-        <v>135866707.15723985</v>
+        <v>58480491.387124024</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="E43" s="11">
         <f>E24+E36+E41</f>
-        <v>1071166797.2689085</v>
+        <v>993780581.49879265</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="E45">
         <f>E43/1000000000</f>
-        <v>1.0711667972689085</v>
+        <v>0.99378058149879267</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">

--- a/Cost model data structure.xlsx
+++ b/Cost model data structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samst\OneDrive\Documents\Work\Projects\PMH web tool\Thailand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB785F5-A9DD-4298-A728-6B3853AA5593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9CE8CD-88A6-4FA8-B5EC-259DA47D8C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="1" r:id="rId1"/>
@@ -3965,7 +3965,7 @@
         <v>246</v>
       </c>
       <c r="E4" s="24">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="F4" s="35" t="s">
         <v>10</v>
@@ -4611,7 +4611,7 @@
         <v>109</v>
       </c>
       <c r="E24" s="13">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="F24" s="34" t="s">
         <v>10</v>
@@ -4646,7 +4646,7 @@
         <v>108</v>
       </c>
       <c r="E25" s="13">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="F25" s="34" t="s">
         <v>9</v>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D2" s="30">
         <f>inputs!E3/(1 - inputs!E4/1000)</f>
-        <v>648841.62895927601</v>
+        <v>647799.41772914364</v>
       </c>
       <c r="E2" s="29" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D2)</f>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D14" s="28">
         <f>D2*inputs!$E$7*inputs!$E$8</f>
-        <v>103814.66063348418</v>
+        <v>103647.90683666299</v>
       </c>
       <c r="E14" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D26" s="28">
         <f>D2*inputs!E7*inputs!E9</f>
-        <v>25953.665158371045</v>
+        <v>25911.976709165749</v>
       </c>
       <c r="E26" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D38" s="28">
         <f>D2*inputs!E10</f>
-        <v>25953.665158371041</v>
+        <v>25911.976709165745</v>
       </c>
       <c r="E38" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="D50" s="28">
         <f>inputs!E24*(D2+D3)/100000</f>
-        <v>51.756841882371049</v>
+        <v>71.108335970602909</v>
       </c>
       <c r="E50" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="D51" s="28">
         <f>(D14*inputs!E17*inputs!E18)/(inputs!E31^0)</f>
-        <v>10277.651402714933</v>
+        <v>10261.142776829636</v>
       </c>
       <c r="E51" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D63" s="28">
         <f>D26*inputs!E17*inputs!E19</f>
-        <v>4269.377918552037</v>
+        <v>4262.5201686577657</v>
       </c>
       <c r="E63" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D75" s="28">
         <f>D38*inputs!E17*inputs!E20</f>
-        <v>862.95936651583713</v>
+        <v>861.57322557976102</v>
       </c>
       <c r="E75" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="D87" s="28">
         <f>D50*inputs!E25</f>
-        <v>3131.2889338834484</v>
+        <v>4266.5001582361747</v>
       </c>
       <c r="E87" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="D88" s="28">
         <f>D51*(inputs!$E$26*inputs!$E$27)</f>
-        <v>36855657.930135749</v>
+        <v>36796457.997711077</v>
       </c>
       <c r="E88" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D100" s="28">
         <f>D63*(inputs!$E$26*inputs!$E$27)</f>
-        <v>15309989.215927605</v>
+        <v>15285397.324806748</v>
       </c>
       <c r="E100" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="D112" s="28">
         <f>D75*(inputs!$E$26*inputs!$E$27)</f>
-        <v>3094572.2883257922</v>
+        <v>3089601.5869290228</v>
       </c>
       <c r="E112" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D124" s="28">
         <f>D87*(inputs!E26*inputs!E27)</f>
-        <v>11228802.116906047</v>
+        <v>15299669.567434922</v>
       </c>
       <c r="E124" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="D125" s="27">
         <f>(D14+D26)*inputs!E28</f>
-        <v>287696378.28054303</v>
+        <v>287234261.82110232</v>
       </c>
       <c r="E125" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="D137" s="28">
         <f>D38*inputs!E29</f>
-        <v>57539275.656108595</v>
+        <v>57446852.364220455</v>
       </c>
       <c r="E137" s="27" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="D149" s="8">
         <f>(D2*inputs!E39*inputs!E50*inputs!E61)-inputs!E32*(D2*inputs!E39*inputs!E50*inputs!E61)</f>
-        <v>31055.247350226251</v>
+        <v>31005.364411002916</v>
       </c>
       <c r="E149" s="7" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D149)</f>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="D150" s="8">
         <f>(D2*inputs!E40*inputs!E51*inputs!E62)-inputs!E32*(D2*inputs!E40*inputs!E51*inputs!E62)</f>
-        <v>21390.751286877829</v>
+        <v>21356.39208392732</v>
       </c>
       <c r="E150" s="7" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D150)</f>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="D355" s="30">
         <f>$D$150*inputs!E72</f>
-        <v>145457.10875076923</v>
+        <v>145223.46617070577</v>
       </c>
       <c r="E355" s="29" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D355)</f>
@@ -17718,7 +17718,7 @@
       </c>
       <c r="D500" s="30">
         <f>D355*(inputs!$E$26*inputs!E27)</f>
-        <v>521609191.98025846</v>
+        <v>520771349.68815088</v>
       </c>
       <c r="E500" s="29" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="D745" s="8">
         <f>D149*inputs!E89</f>
-        <v>16335060.106219009</v>
+        <v>16308821.680187535</v>
       </c>
       <c r="E745" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="D746" s="8">
         <f>D150*inputs!E90</f>
-        <v>9518884.3226606343</v>
+        <v>9503594.4773476571</v>
       </c>
       <c r="E746" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -27806,7 +27806,7 @@
       </c>
       <c r="E4" s="11">
         <f>SUM(computations!D51:D74)</f>
-        <v>52455.76336188092</v>
+        <v>52432.396986101347</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="E5" s="11">
         <f>SUM(computations!D88:D111)</f>
-        <v>188106367.41570503</v>
+        <v>188022575.59215948</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="E6" s="11">
         <f>SUM(computations!D75:D87)</f>
-        <v>9616.3063148971178</v>
+        <v>10750.131398313768</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -27851,7 +27851,7 @@
       </c>
       <c r="E7" s="11">
         <f>SUM(computations!D112:D123)</f>
-        <v>23255272.32831502</v>
+        <v>23250301.626918249</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="E8" s="11">
         <f>computations!D87</f>
-        <v>3131.2889338834484</v>
+        <v>4266.5001582361747</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="E9" s="11">
         <f>computations!D124</f>
-        <v>11228802.116906047</v>
+        <v>15299669.567434922</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="E10" s="11">
         <f>SUM(computations!D125:D136)</f>
-        <v>683751477.64804518</v>
+        <v>683289361.18860447</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -27911,7 +27911,7 @@
       </c>
       <c r="E11" s="11">
         <f>SUM(computations!D137:D148)</f>
-        <v>255390818.60971653</v>
+        <v>255298395.31782839</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="E12" s="11">
         <f>SUM(computations!D355:D499)</f>
-        <v>185386.5222109966</v>
+        <v>185152.87963093314</v>
       </c>
     </row>
     <row r="13" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="E24" s="11">
         <f>SUM(computations!D500:D644)</f>
-        <v>664796068.64863372</v>
+        <v>663958226.35652614</v>
       </c>
     </row>
     <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="E41" s="11">
         <f>SUM(computations!D745:D751)</f>
-        <v>58480491.387124024</v>
+        <v>58438963.115779579</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -28298,7 +28298,7 @@
       </c>
       <c r="E42" s="11">
         <f>E5+E6+E7+E9+E10+E11</f>
-        <v>1161742354.4250026</v>
+        <v>1165171053.4243438</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="E43" s="11">
         <f>E24+E36+E41</f>
-        <v>993780581.49879265</v>
+        <v>992901210.93534064</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="E44">
         <f>E42/1000000000</f>
-        <v>1.1617423544250025</v>
+        <v>1.1651710534243438</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="E45">
         <f>E43/1000000000</f>
-        <v>0.99378058149879267</v>
+        <v>0.99290121093534067</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="E56" s="11">
         <f>SUM(E5+E7+E9)/1000000</f>
-        <v>222.59044186092609</v>
+        <v>226.57254678651267</v>
       </c>
       <c r="F56" t="s">
         <v>823</v>

--- a/Cost model data structure.xlsx
+++ b/Cost model data structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samst\OneDrive\Documents\Work\Projects\PMH web tool\Thailand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9CE8CD-88A6-4FA8-B5EC-259DA47D8C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B6F5B-EE2F-4A4D-93B1-4245BDBED76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="1056">
   <si>
     <t>Section</t>
   </si>
@@ -3299,6 +3299,12 @@
   </si>
   <si>
     <t>Valuing healthcare age 0-1, in USD</t>
+  </si>
+  <si>
+    <t>Mother's DALY</t>
+  </si>
+  <si>
+    <t>Mother's Income loss</t>
   </si>
 </sst>
 </file>
@@ -3387,7 +3393,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3430,6 +3436,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3444,7 +3456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3487,6 +3499,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4172,8 +4189,8 @@
       <c r="D10" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="E10" s="25">
-        <v>0.04</v>
+      <c r="E10" s="23">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="F10" s="35" t="s">
         <v>10</v>
@@ -4517,23 +4534,25 @@
       <c r="C21" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="39">
         <f>1-E18</f>
         <v>0.60399999999999998</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="38" t="s">
         <v>241</v>
       </c>
       <c r="L21" s="12" t="s">
@@ -4547,23 +4566,25 @@
       <c r="C22" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="39">
         <f>1-E19</f>
         <v>0.34199999999999997</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="38" t="s">
         <v>242</v>
       </c>
       <c r="L22" s="12" t="s">
@@ -4577,23 +4598,25 @@
       <c r="C23" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="39">
         <f>1-E22</f>
         <v>0.65800000000000003</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="38" t="s">
         <v>247</v>
       </c>
       <c r="L23" s="12" t="s">
@@ -6440,15 +6463,17 @@
       <c r="C79" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="E79" s="15">
-        <v>0</v>
-      </c>
-      <c r="F79" s="35" t="s">
+      <c r="E79" s="39">
+        <v>0</v>
+      </c>
+      <c r="F79" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
       <c r="I79" s="14" t="s">
         <v>28</v>
       </c>
@@ -6472,16 +6497,18 @@
       <c r="C80" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="38" t="s">
         <v>487</v>
       </c>
-      <c r="E80" s="15">
+      <c r="E80" s="39">
         <f>(1-E73)</f>
         <v>0.96399999999999997</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
       <c r="I80" s="14" t="s">
         <v>28</v>
       </c>
@@ -6502,16 +6529,18 @@
       <c r="C81" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="38" t="s">
         <v>488</v>
       </c>
-      <c r="E81" s="15">
+      <c r="E81" s="39">
         <f>(1-E74)</f>
         <v>0.86699999999999999</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
       <c r="I81" s="14" t="s">
         <v>28</v>
       </c>
@@ -6532,16 +6561,18 @@
       <c r="C82" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E82" s="15">
+      <c r="E82" s="39">
         <f>(1-E75)</f>
         <v>0.872</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
       <c r="I82" s="14" t="s">
         <v>28</v>
       </c>
@@ -6562,16 +6593,18 @@
       <c r="C83" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="38" t="s">
         <v>490</v>
       </c>
-      <c r="E83" s="15">
+      <c r="E83" s="39">
         <f>(1-E76)</f>
         <v>0.75900000000000001</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
       <c r="I83" s="14" t="s">
         <v>28</v>
       </c>
@@ -6592,16 +6625,18 @@
       <c r="C84" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="38" t="s">
         <v>491</v>
       </c>
-      <c r="E84" s="15">
+      <c r="E84" s="39">
         <f t="shared" ref="E84:E85" si="0">(1-E77)</f>
         <v>0.95499999999999996</v>
       </c>
-      <c r="F84" s="35" t="s">
+      <c r="F84" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G84" s="40"/>
+      <c r="H84" s="40"/>
       <c r="I84" s="14" t="s">
         <v>28</v>
       </c>
@@ -6622,16 +6657,18 @@
       <c r="C85" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="38" t="s">
         <v>492</v>
       </c>
-      <c r="E85" s="15">
+      <c r="E85" s="39">
         <f t="shared" si="0"/>
         <v>0.73499999999999999</v>
       </c>
-      <c r="F85" s="35" t="s">
+      <c r="F85" s="38" t="s">
         <v>9</v>
       </c>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
       <c r="I85" s="14" t="s">
         <v>28</v>
       </c>
@@ -8916,7 +8953,7 @@
       </c>
       <c r="D38" s="28">
         <f>D2*inputs!E10</f>
-        <v>25911.976709165745</v>
+        <v>22672.979620520029</v>
       </c>
       <c r="E38" s="27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9619,7 +9656,7 @@
       </c>
       <c r="D75" s="28">
         <f>D38*inputs!E17*inputs!E20</f>
-        <v>861.57322557976102</v>
+        <v>753.87657238229099</v>
       </c>
       <c r="E75" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10322,7 +10359,7 @@
       </c>
       <c r="D112" s="28">
         <f>D75*(inputs!$E$26*inputs!$E$27)</f>
-        <v>3089601.5869290228</v>
+        <v>2703401.3885628954</v>
       </c>
       <c r="E112" s="27" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -10797,7 +10834,7 @@
       </c>
       <c r="D137" s="28">
         <f>D38*inputs!E29</f>
-        <v>57446852.364220455</v>
+        <v>50265995.818692908</v>
       </c>
       <c r="E137" s="27" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27770,7 +27807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE09E027-07AB-5B4E-B150-E88615AE26EE}">
-  <dimension ref="B2:F56"/>
+  <dimension ref="B2:G56"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.5" customWidth="1"/>
@@ -27836,7 +27873,7 @@
       </c>
       <c r="E6" s="11">
         <f>SUM(computations!D75:D87)</f>
-        <v>10750.131398313768</v>
+        <v>10642.434745116298</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -27851,7 +27888,7 @@
       </c>
       <c r="E7" s="11">
         <f>SUM(computations!D112:D123)</f>
-        <v>23250301.626918249</v>
+        <v>22864101.428552121</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -27911,7 +27948,7 @@
       </c>
       <c r="E11" s="11">
         <f>SUM(computations!D137:D148)</f>
-        <v>255298395.31782839</v>
+        <v>248117538.77230087</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -27977,7 +28014,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>770</v>
       </c>
@@ -27989,7 +28026,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>770</v>
       </c>
@@ -28001,7 +28038,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>770</v>
       </c>
@@ -28013,7 +28050,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>770</v>
       </c>
@@ -28025,7 +28062,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>770</v>
       </c>
@@ -28037,7 +28074,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>770</v>
       </c>
@@ -28049,7 +28086,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>770</v>
       </c>
@@ -28061,7 +28098,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>771</v>
       </c>
@@ -28075,8 +28112,11 @@
         <f>SUM(computations!D500:D644)</f>
         <v>663958226.35652614</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>771</v>
       </c>
@@ -28088,7 +28128,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>771</v>
       </c>
@@ -28100,7 +28140,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>771</v>
       </c>
@@ -28112,7 +28152,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>771</v>
       </c>
@@ -28124,7 +28164,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>771</v>
       </c>
@@ -28136,7 +28176,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>771</v>
       </c>
@@ -28148,7 +28188,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>771</v>
       </c>
@@ -28160,7 +28200,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>771</v>
       </c>
@@ -28172,7 +28212,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>771</v>
       </c>
@@ -28184,7 +28224,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>771</v>
       </c>
@@ -28196,7 +28236,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>771</v>
       </c>
@@ -28208,7 +28248,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>772</v>
       </c>
@@ -28222,8 +28262,12 @@
         <f>SUM(computations!D645:D744)</f>
         <v>270504021.46303487</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G36" s="11">
+        <f>E7+E5+E9</f>
+        <v>226186346.58814651</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>772</v>
       </c>
@@ -28235,7 +28279,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>772</v>
       </c>
@@ -28247,7 +28291,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>772</v>
       </c>
@@ -28259,7 +28303,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>772</v>
       </c>
@@ -28271,7 +28315,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>758</v>
       </c>
@@ -28285,8 +28329,11 @@
         <f>SUM(computations!D745:D751)</f>
         <v>58438963.115779579</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="G41" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>774</v>
       </c>
@@ -28296,12 +28343,16 @@
       <c r="D42" t="s">
         <v>774</v>
       </c>
-      <c r="E42" s="11">
-        <f>E5+E6+E7+E9+E10+E11</f>
-        <v>1165171053.4243438</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E42" s="41">
+        <f>E5+E7+E9+E10+E11</f>
+        <v>1157593246.549052</v>
+      </c>
+      <c r="G42" s="11">
+        <f>E10+E11</f>
+        <v>931406899.96090531</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>773</v>
       </c>
@@ -28316,7 +28367,7 @@
         <v>992901210.93534064</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>774</v>
       </c>
@@ -28326,12 +28377,12 @@
       <c r="D44" t="s">
         <v>804</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="42">
         <f>E42/1000000000</f>
-        <v>1.1651710534243438</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+        <v>1.1575932465490519</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>773</v>
       </c>
@@ -28352,7 +28403,7 @@
       </c>
       <c r="E56" s="11">
         <f>SUM(E5+E7+E9)/1000000</f>
-        <v>226.57254678651267</v>
+        <v>226.18634658814651</v>
       </c>
       <c r="F56" t="s">
         <v>823</v>

--- a/Cost model data structure.xlsx
+++ b/Cost model data structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samst\OneDrive\Documents\Work\Projects\PMH web tool\Thailand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B6F5B-EE2F-4A4D-93B1-4245BDBED76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18328A5B-EB48-40CC-8EC4-1C4EE9D01CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0D2E9C17-1371-9741-AFE8-B54FBA3315B4}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="1" r:id="rId1"/>
@@ -3311,10 +3311,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -3456,7 +3457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3502,8 +3503,11 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6260,7 +6264,7 @@
       <c r="D72" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="21">
         <v>6.8</v>
       </c>
       <c r="F72" s="35" t="s">
@@ -6762,7 +6766,7 @@
       <c r="D88" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="E88" s="20">
+      <c r="E88" s="13">
         <v>900</v>
       </c>
       <c r="F88" s="35" t="s">
@@ -8264,7 +8268,7 @@
       <c r="C2" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="42">
         <f>inputs!E3/(1 - inputs!E4/1000)</f>
         <v>647799.41772914364</v>
       </c>
@@ -8286,7 +8290,7 @@
       <c r="C3" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="43">
         <f>inputs!E3-inputs!E5*inputs!E3</f>
         <v>645079.41810000001</v>
       </c>
@@ -9179,7 +9183,7 @@
       <c r="C50" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="41">
         <f>inputs!E24*(D2+D3)/100000</f>
         <v>71.108335970602909</v>
       </c>
@@ -10642,11 +10646,11 @@
       <c r="C127" s="27" t="s">
         <v>826</v>
       </c>
-      <c r="D127" s="28">
+      <c r="D127" s="44">
         <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^2)</f>
         <v>13471014.904126221</v>
       </c>
-      <c r="E127" s="27" t="str">
+      <c r="E127" s="40" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^2)</v>
       </c>
@@ -10661,13 +10665,13 @@
       <c r="C128" s="27" t="s">
         <v>827</v>
       </c>
-      <c r="D128" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^3)</f>
-        <v>13078655.246724486</v>
-      </c>
-      <c r="E128" s="27" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^3)</v>
+      <c r="D128" s="44">
+        <f>(($D$17+$D$29)*inputs!$E$28)/(inputs!$E$31^3)</f>
+        <v>13069500.188051781</v>
+      </c>
+      <c r="E128" s="40" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D128)</f>
+        <v>=(($D$17+$D$29)*inputs!$E$28)/(inputs!$E$31^3)</v>
       </c>
     </row>
     <row r="129" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10680,13 +10684,13 @@
       <c r="C129" s="27" t="s">
         <v>828</v>
       </c>
-      <c r="D129" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^4)</f>
-        <v>12697723.540509211</v>
-      </c>
-      <c r="E129" s="27" t="str">
+      <c r="D129" s="44">
+        <f>(($D$18+$D$30)*inputs!$E$28)/(inputs!$E$31^4)</f>
+        <v>12679952.949437035</v>
+      </c>
+      <c r="E129" s="40" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^4)</v>
+        <v>=(($D$18+$D$30)*inputs!$E$28)/(inputs!$E$31^4)</v>
       </c>
     </row>
     <row r="130" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10699,13 +10703,13 @@
       <c r="C130" s="27" t="s">
         <v>829</v>
       </c>
-      <c r="D130" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^5)</f>
-        <v>12327886.932533214</v>
-      </c>
-      <c r="E130" s="27" t="str">
+      <c r="D130" s="44">
+        <f>(($D$19+$D$31)*inputs!$E$28)/(inputs!$E$31^5)</f>
+        <v>12302016.487740226</v>
+      </c>
+      <c r="E130" s="40" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^5)</v>
+        <v>=(($D$19+$D$31)*inputs!$E$28)/(inputs!$E$31^5)</v>
       </c>
     </row>
     <row r="131" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10718,13 +10722,13 @@
       <c r="C131" s="27" t="s">
         <v>830</v>
       </c>
-      <c r="D131" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^6)</f>
-        <v>11968822.264595354</v>
-      </c>
-      <c r="E131" s="27" t="str">
+      <c r="D131" s="44">
+        <f>(($D$20+$D$32)*inputs!$E$28)/(inputs!$E$31^6)</f>
+        <v>11935344.734173598</v>
+      </c>
+      <c r="E131" s="40" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^6)</v>
+        <v>=(($D$20+$D$32)*inputs!$E$28)/(inputs!$E$31^6)</v>
       </c>
     </row>
     <row r="132" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10737,13 +10741,13 @@
       <c r="C132" s="27" t="s">
         <v>831</v>
       </c>
-      <c r="D132" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^7)</f>
-        <v>11620215.790869275</v>
-      </c>
-      <c r="E132" s="27" t="str">
+      <c r="D132" s="44">
+        <f>(($D$21+$D$33)*inputs!$E$28)/(inputs!$E$31^7)</f>
+        <v>11579601.934815221</v>
+      </c>
+      <c r="E132" s="40" t="str">
         <f t="shared" ref="E132:E148" ca="1" si="2">_xlfn.FORMULATEXT(D132)</f>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^7)</v>
+        <v>=(($D$21+$D$33)*inputs!$E$28)/(inputs!$E$31^7)</v>
       </c>
     </row>
     <row r="133" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10756,13 +10760,13 @@
       <c r="C133" s="27" t="s">
         <v>832</v>
       </c>
-      <c r="D133" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^8)</f>
-        <v>11281762.903756578</v>
-      </c>
-      <c r="E133" s="27" t="str">
+      <c r="D133" s="44">
+        <f>(($D$22+$D$34)*inputs!$E$28)/(inputs!$E$31^8)</f>
+        <v>11234462.343165873</v>
+      </c>
+      <c r="E133" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^8)</v>
+        <v>=(($D$22+$D$34)*inputs!$E$28)/(inputs!$E$31^8)</v>
       </c>
     </row>
     <row r="134" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10775,13 +10779,13 @@
       <c r="C134" s="27" t="s">
         <v>833</v>
       </c>
-      <c r="D134" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^9)</f>
-        <v>10953167.867724832</v>
-      </c>
-      <c r="E134" s="27" t="str">
+      <c r="D134" s="44">
+        <f>(($D$23+$D$35)*inputs!$E$28)/(inputs!$E$31^9)</f>
+        <v>10899609.921869569</v>
+      </c>
+      <c r="E134" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^9)</v>
+        <v>=(($D$23+$D$35)*inputs!$E$28)/(inputs!$E$31^9)</v>
       </c>
     </row>
     <row r="135" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10794,13 +10798,13 @@
       <c r="C135" s="27" t="s">
         <v>834</v>
       </c>
-      <c r="D135" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^10)</f>
-        <v>10634143.560897896</v>
-      </c>
-      <c r="E135" s="27" t="str">
+      <c r="D135" s="44">
+        <f>(($D$24+$D$36)*inputs!$E$28)/(inputs!$E$31^10)</f>
+        <v>10574738.053324526</v>
+      </c>
+      <c r="E135" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^10)</v>
+        <v>=(($D$24+$D$36)*inputs!$E$28)/(inputs!$E$31^10)</v>
       </c>
     </row>
     <row r="136" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -10813,13 +10817,13 @@
       <c r="C136" s="27" t="s">
         <v>835</v>
       </c>
-      <c r="D136" s="28">
-        <f>(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^11)</f>
-        <v>10324411.224172715</v>
-      </c>
-      <c r="E136" s="27" t="str">
+      <c r="D136" s="44">
+        <f>(($D$25+$D$37)*inputs!$E$28)/(inputs!$E$31^11)</f>
+        <v>10259549.258919608</v>
+      </c>
+      <c r="E136" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>=(($D$16+$D$28)*inputs!$E$28)/(inputs!$E$31^11)</v>
+        <v>=(($D$25+$D$37)*inputs!$E$28)/(inputs!$E$31^11)</v>
       </c>
     </row>
     <row r="137" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -11079,7 +11083,7 @@
       <c r="C150" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150" s="45">
         <f>(D2*inputs!E40*inputs!E51*inputs!E62)-inputs!E32*(D2*inputs!E40*inputs!E51*inputs!E62)</f>
         <v>21356.39208392732</v>
       </c>
@@ -11712,13 +11716,13 @@
       <c r="C183" s="32" t="s">
         <v>314</v>
       </c>
-      <c r="D183" s="33">
-        <f>D182-D182*inputs!$E$37</f>
-        <v>27030.078881310335</v>
-      </c>
-      <c r="E183" s="32" t="str">
+      <c r="D183" s="44">
+        <f>D182-D182*inputs!$E$36</f>
+        <v>27057.163128686396</v>
+      </c>
+      <c r="E183" s="40" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>=D182-D182*inputs!$E$37</v>
+        <v>=D182-D182*inputs!$E$36</v>
       </c>
     </row>
     <row r="184" spans="1:5" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11733,7 +11737,7 @@
       </c>
       <c r="D184" s="33">
         <f>D183-D183*inputs!$E$37</f>
-        <v>26976.018723547713</v>
+        <v>27003.048802429024</v>
       </c>
       <c r="E184" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11752,7 +11756,7 @@
       </c>
       <c r="D185" s="33">
         <f>D184-D184*inputs!$E$37</f>
-        <v>26922.066686100618</v>
+        <v>26949.042704824165</v>
       </c>
       <c r="E185" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11771,7 +11775,7 @@
       </c>
       <c r="D186" s="33">
         <f>D185-D185*inputs!$E$37</f>
-        <v>26868.222552728417</v>
+        <v>26895.144619414517</v>
       </c>
       <c r="E186" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11790,7 +11794,7 @@
       </c>
       <c r="D187" s="33">
         <f>D186-D186*inputs!$E$37</f>
-        <v>26814.486107622961</v>
+        <v>26841.354330175687</v>
       </c>
       <c r="E187" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11809,7 +11813,7 @@
       </c>
       <c r="D188" s="33">
         <f>D187-D187*inputs!$E$38</f>
-        <v>26760.857135407714</v>
+        <v>26787.671621515336</v>
       </c>
       <c r="E188" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11828,7 +11832,7 @@
       </c>
       <c r="D189" s="33">
         <f>D188-D188*inputs!$E$38</f>
-        <v>26707.335421136897</v>
+        <v>26734.096278272304</v>
       </c>
       <c r="E189" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11847,7 +11851,7 @@
       </c>
       <c r="D190" s="33">
         <f>D189-D189*inputs!$E$38</f>
-        <v>26653.920750294623</v>
+        <v>26680.628085715758</v>
       </c>
       <c r="E190" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11866,7 +11870,7 @@
       </c>
       <c r="D191" s="33">
         <f>D190-D190*inputs!$E$38</f>
-        <v>26600.612908794035</v>
+        <v>26627.266829544325</v>
       </c>
       <c r="E191" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11885,7 +11889,7 @@
       </c>
       <c r="D192" s="33">
         <f>D191-D191*inputs!$E$38</f>
-        <v>26547.411682976446</v>
+        <v>26574.012295885237</v>
       </c>
       <c r="E192" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11904,7 +11908,7 @@
       </c>
       <c r="D193" s="33">
         <f>D192-D192*inputs!$E$38</f>
-        <v>26494.316859610492</v>
+        <v>26520.864271293467</v>
       </c>
       <c r="E193" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11923,7 +11927,7 @@
       </c>
       <c r="D194" s="33">
         <f>D193-D193*inputs!$E$38</f>
-        <v>26441.32822589127</v>
+        <v>26467.822542750881</v>
       </c>
       <c r="E194" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11942,7 +11946,7 @@
       </c>
       <c r="D195" s="33">
         <f>D194-D194*inputs!$E$38</f>
-        <v>26388.445569439486</v>
+        <v>26414.886897665379</v>
       </c>
       <c r="E195" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11961,7 +11965,7 @@
       </c>
       <c r="D196" s="33">
         <f>D195-D195*inputs!$E$38</f>
-        <v>26335.668678300608</v>
+        <v>26362.05712387005</v>
       </c>
       <c r="E196" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11980,7 +11984,7 @@
       </c>
       <c r="D197" s="33">
         <f>D196-D196*inputs!$E$38</f>
-        <v>26282.997340944006</v>
+        <v>26309.333009622311</v>
       </c>
       <c r="E197" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11999,7 +12003,7 @@
       </c>
       <c r="D198" s="33">
         <f>D197-D197*inputs!$E$38</f>
-        <v>26230.431346262118</v>
+        <v>26256.714343603067</v>
       </c>
       <c r="E198" s="32" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -20792,7 +20796,7 @@
       </c>
       <c r="D654" s="8">
         <f>(D183*inputs!$E$88)/(inputs!$E$31^inputs!E120)</f>
-        <v>11618744.590166209</v>
+        <v>11630386.618813667</v>
       </c>
       <c r="E654" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20811,7 +20815,7 @@
       </c>
       <c r="D655" s="8">
         <f>(D184*inputs!$E$88)/(inputs!$E$31^inputs!E121)</f>
-        <v>11257773.884452306</v>
+        <v>11269054.219005864</v>
       </c>
       <c r="E655" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20830,7 +20834,7 @@
       </c>
       <c r="D656" s="8">
         <f>(D185*inputs!$E$88)/(inputs!$E$31^inputs!E122)</f>
-        <v>10908017.802605243</v>
+        <v>10918947.680162964</v>
       </c>
       <c r="E656" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20849,7 +20853,7 @@
       </c>
       <c r="D657" s="8">
         <f>(D186*inputs!$E$88)/(inputs!$E$31^inputs!E123)</f>
-        <v>10569127.929126246</v>
+        <v>10579718.237672465</v>
       </c>
       <c r="E657" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20868,7 +20872,7 @@
       </c>
       <c r="D658" s="8">
         <f>(D187*inputs!$E$88)/(inputs!$E$31^inputs!E124)</f>
-        <v>10240766.673075724</v>
+        <v>10251027.962327302</v>
       </c>
       <c r="E658" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20887,7 +20891,7 @@
       </c>
       <c r="D659" s="8">
         <f>(D188*inputs!$E$88)/(inputs!$E$31^inputs!E125)</f>
-        <v>9922606.9317762833</v>
+        <v>9932549.4236918911</v>
       </c>
       <c r="E659" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20906,7 +20910,7 @@
       </c>
       <c r="D660" s="8">
         <f>(D189*inputs!$E$88)/(inputs!$E$31^inputs!E126)</f>
-        <v>9614331.7649638131</v>
+        <v>9623965.3639267031</v>
       </c>
       <c r="E660" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20925,7 +20929,7 @@
       </c>
       <c r="D661" s="8">
         <f>(D190*inputs!$E$88)/(inputs!$E$31^inputs!E127)</f>
-        <v>9315634.0790620279</v>
+        <v>9324968.3817464579</v>
       </c>
       <c r="E661" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20944,7 +20948,7 @@
       </c>
       <c r="D662" s="8">
         <f>(D191*inputs!$E$88)/(inputs!$E$31^inputs!E128)</f>
-        <v>9026216.3212659266</v>
+        <v>9035260.6261970531</v>
       </c>
       <c r="E662" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20963,7 +20967,7 @@
       </c>
       <c r="D663" s="8">
         <f>(D192*inputs!$E$88)/(inputs!$E$31^inputs!E129)</f>
-        <v>8745790.1831295099</v>
+        <v>8754553.4999462701</v>
       </c>
       <c r="E663" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20982,7 +20986,7 @@
       </c>
       <c r="D664" s="8">
         <f>(D193*inputs!$E$88)/(inputs!$E$31^inputs!E130)</f>
-        <v>8474076.3133623768</v>
+        <v>8482567.3717926014</v>
       </c>
       <c r="E664" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -21001,7 +21005,7 @@
       </c>
       <c r="D665" s="8">
         <f>(D194*inputs!$E$88)/(inputs!$E$31^inputs!E131)</f>
-        <v>8210804.0395491784</v>
+        <v>8219031.2981058406</v>
       </c>
       <c r="E665" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -21020,7 +21024,7 @@
       </c>
       <c r="D666" s="8">
         <f>(D195*inputs!$E$88)/(inputs!$E$31^inputs!E132)</f>
-        <v>7955711.0985146407</v>
+        <v>7963682.7529219706</v>
       </c>
       <c r="E666" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -21039,7 +21043,7 @@
       </c>
       <c r="D667" s="8">
         <f>(D196*inputs!$E$88)/(inputs!$E$31^inputs!E133)</f>
-        <v>7708543.3750656424</v>
+        <v>7716267.3664234243</v>
       </c>
       <c r="E667" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -21058,7 +21062,7 @@
       </c>
       <c r="D668" s="8">
         <f>(D197*inputs!$E$88)/(inputs!$E$31^inputs!E134)</f>
-        <v>7469054.6488500098</v>
+        <v>7476538.6715442492</v>
       </c>
       <c r="E668" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -21077,7 +21081,7 @@
       </c>
       <c r="D669" s="8">
         <f>(D198*inputs!$E$88)/(inputs!$E$31^inputs!E135)</f>
-        <v>7237006.3490799135</v>
+        <v>7244257.8584477305</v>
       </c>
       <c r="E669" s="7" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -27933,7 +27937,7 @@
       </c>
       <c r="E10" s="11">
         <f>SUM(computations!D125:D136)</f>
-        <v>683289361.18860447</v>
+        <v>682937347.72831833</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -28086,7 +28090,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>770</v>
       </c>
@@ -28260,7 +28264,7 @@
       </c>
       <c r="E36" s="11">
         <f>SUM(computations!D645:D744)</f>
-        <v>270504021.46303487</v>
+        <v>270652592.81171632</v>
       </c>
       <c r="G36" s="11">
         <f>E7+E5+E9</f>
@@ -28343,13 +28347,13 @@
       <c r="D42" t="s">
         <v>774</v>
       </c>
-      <c r="E42" s="41">
+      <c r="E42" s="11">
         <f>E5+E7+E9+E10+E11</f>
-        <v>1157593246.549052</v>
+        <v>1157241233.0887659</v>
       </c>
       <c r="G42" s="11">
         <f>E10+E11</f>
-        <v>931406899.96090531</v>
+        <v>931054886.50061917</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
@@ -28364,7 +28368,7 @@
       </c>
       <c r="E43" s="11">
         <f>E24+E36+E41</f>
-        <v>992901210.93534064</v>
+        <v>993049782.28402209</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
@@ -28377,9 +28381,9 @@
       <c r="D44" t="s">
         <v>804</v>
       </c>
-      <c r="E44" s="42">
+      <c r="E44">
         <f>E42/1000000000</f>
-        <v>1.1575932465490519</v>
+        <v>1.1572412330887658</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -28394,7 +28398,7 @@
       </c>
       <c r="E45">
         <f>E43/1000000000</f>
-        <v>0.99290121093534067</v>
+        <v>0.99304978228402208</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
